--- a/Sindhi Muslim/HR Data/HR SMB Staff Data - 3rd Year 3rd QTR.xlsx
+++ b/Sindhi Muslim/HR Data/HR SMB Staff Data - 3rd Year 3rd QTR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\HR Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0ED29DD-FFCC-40DC-A39F-793EA114DADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DED40C2E-2958-4DEE-BB18-59F0ABCE37B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="HR Data Sheet " sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HR Data Sheet '!$A$5:$AT$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HR Data Sheet '!$A$5:$S$37</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -361,9 +361,6 @@
     <t>New Appointment</t>
   </si>
   <si>
-    <t>Contunue</t>
-  </si>
-  <si>
     <t>Mehek</t>
   </si>
   <si>
@@ -407,6 +404,9 @@
   </si>
   <si>
     <t>Group</t>
+  </si>
+  <si>
+    <t>Saba Din</t>
   </si>
 </sst>
 </file>
@@ -904,7 +904,7 @@
     </row>
     <row r="3" spans="1:46" ht="18.75">
       <c r="A3" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -1168,7 +1168,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>31</v>
+        <v>123</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>32</v>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="Q8" s="4"/>
       <c r="R8" s="4" t="s">
-        <v>108</v>
+        <v>24</v>
       </c>
       <c r="S8" s="7"/>
       <c r="T8" s="5"/>
@@ -3002,13 +3002,13 @@
         <v>27</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>95</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H32" s="4" t="s">
         <v>104</v>
@@ -3038,10 +3038,10 @@
         <v>28</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>33</v>
@@ -3072,10 +3072,10 @@
         <v>29</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>33</v>
@@ -3106,10 +3106,10 @@
         <v>30</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>33</v>
@@ -3140,10 +3140,10 @@
         <v>31</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>52</v>
@@ -3152,10 +3152,10 @@
         <v>103</v>
       </c>
       <c r="I36" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="N36" s="4" t="s">
         <v>122</v>
-      </c>
-      <c r="N36" s="4" t="s">
-        <v>123</v>
       </c>
       <c r="O36" s="8">
         <v>45768</v>
@@ -3174,10 +3174,10 @@
         <v>32</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>27</v>
@@ -3186,10 +3186,10 @@
         <v>103</v>
       </c>
       <c r="I37" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="N37" s="4" t="s">
         <v>122</v>
-      </c>
-      <c r="N37" s="4" t="s">
-        <v>123</v>
       </c>
       <c r="O37" s="8">
         <v>45778</v>
@@ -3204,7 +3204,7 @@
       <c r="S37" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:AT37" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A5:S37" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="7">
       <filters>
         <filter val="Non-Teaching"/>
@@ -3213,7 +3213,6 @@
     <filterColumn colId="17">
       <filters>
         <filter val="continue"/>
-        <filter val="Contunue"/>
         <filter val="New Appointment"/>
       </filters>
     </filterColumn>
